--- a/DMart_Retail_dataset.xlsx
+++ b/DMart_Retail_dataset.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sheela Maurya\Desktop\Data science\Excel\DMart analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A18CBDF-C007-4851-BE89-CEAFBC1211CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979CF4F1-3408-437C-A90C-C772F3685CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
@@ -1693,32 +1704,38 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1777,23 +1794,106 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="28">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2019,6 +2119,23 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FF000000"/>
@@ -2091,23 +2208,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF96309A-774D-41F6-9F78-CE839F277E15}" name="Table1" displayName="Table1" ref="A1:N499" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF96309A-774D-41F6-9F78-CE839F277E15}" name="Table1" displayName="Table1" ref="A1:N499" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24">
   <autoFilter ref="A1:N499" xr:uid="{BF96309A-774D-41F6-9F78-CE839F277E15}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{C98EE2D8-5A01-45BB-83AF-9E6E2D2CFB66}" name="Column1" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{C06D5063-30DF-4E18-8966-06E13FE0E541}" name="Updated region" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{BCFD60C6-27FB-4B98-A114-7D35B815F8E5}" name="Region" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{0C89477E-B8DD-4F1E-BE07-D0EEB9257EC8}" name="Category" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{EC154C11-B037-4253-B0CB-017EE4B4DBCC}" name="sales" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{7CAF5FA2-78E0-44B0-9CD5-C58D1F81A319}" name="discount" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{380EE3AE-DF9E-4B3E-A7F4-9C87112114E2}" name="quantity" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{DDA9F4C1-1507-4ACE-9962-F72D01AE6E6E}" name="order_date" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{D3A06104-A437-448F-8EF5-F9A764070FBD}" name="delivery_date" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{632EBC1D-824D-42BF-999D-9B9DABB170B1}" name="customer_type2" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{691CE09C-FC7D-4E79-8298-D0738D346C32}" name="payment_mode" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{CF881AD6-8845-4457-8231-F0286F8B4951}" name="profit" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{0D813739-41C6-4FFE-9D09-F54B21C85D07}" name="Updated city" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{A57E5903-AD66-497A-A025-E8BA3D88243B}" name="city" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C98EE2D8-5A01-45BB-83AF-9E6E2D2CFB66}" name="Column1" dataDxfId="23"/>
+    <tableColumn id="15" xr3:uid="{C06D5063-30DF-4E18-8966-06E13FE0E541}" name="Updated region" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{BCFD60C6-27FB-4B98-A114-7D35B815F8E5}" name="Region" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{0C89477E-B8DD-4F1E-BE07-D0EEB9257EC8}" name="Category" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{EC154C11-B037-4253-B0CB-017EE4B4DBCC}" name="sales" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{7CAF5FA2-78E0-44B0-9CD5-C58D1F81A319}" name="discount" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{380EE3AE-DF9E-4B3E-A7F4-9C87112114E2}" name="quantity" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{DDA9F4C1-1507-4ACE-9962-F72D01AE6E6E}" name="order_date" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{D3A06104-A437-448F-8EF5-F9A764070FBD}" name="delivery_date" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{632EBC1D-824D-42BF-999D-9B9DABB170B1}" name="customer_type2" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{691CE09C-FC7D-4E79-8298-D0738D346C32}" name="payment_mode" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{CF881AD6-8845-4457-8231-F0286F8B4951}" name="profit" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{0D813739-41C6-4FFE-9D09-F54B21C85D07}" name="Updated city" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{A57E5903-AD66-497A-A025-E8BA3D88243B}" name="city" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -45304,6 +45421,26 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
+  <conditionalFormatting sqref="E1:E499">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F499">
+    <cfRule type="top10" dxfId="0" priority="4" rank="20"/>
+    <cfRule type="top10" dxfId="1" priority="2" rank="10"/>
+    <cfRule type="top10" dxfId="2" priority="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="top10" dxfId="6" priority="3" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="1">
